--- a/data/trans_orig/IQ2606_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R2-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45419</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38010</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52888</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>56774</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48888</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>63944</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49001</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>63717</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45419</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37511</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>52759</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91720</t>
+          <t>91291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113282</t>
+          <t>112493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32676</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47554</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33346</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26176</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41232</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26403</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41119</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40145</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>32805</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48053</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62402</t>
+          <t>63191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83964</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,67 +1070,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>262567</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>244780</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>281719</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>259347</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>242402</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>275833</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>243494</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>276056</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>59,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>62,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>262567</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>244172</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>279221</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,18%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>496201</t>
+          <t>497318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>545200</t>
+          <t>547131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>213259</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>194107</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>231046</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>180057</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>163571</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>197002</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>163348</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>195910</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>40,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>213259</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>196605</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>231654</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>370029</t>
+          <t>368098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419028</t>
+          <t>417911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475826</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475826</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475826</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>635</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>439404</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>439404</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>439404</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>475826</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>475826</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>475826</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,74 +1408,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>109025</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98958</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>118035</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>112314</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>101987</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121652</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>102509</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>121643</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>63,99%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>75,94%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>109025</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98245</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>118223</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,71%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>60,11%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>72,34%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>313</t>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207206</t>
+          <t>207991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235314</t>
+          <t>235333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54411</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45401</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>64478</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>47874</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38536</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>58201</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38545</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57679</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>24,06%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>54411</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45213</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65191</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,29%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88309</t>
+          <t>88290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116417</t>
+          <t>115632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>160188</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>417010</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>396288</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>440769</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>57,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>407089</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>448689</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>404431</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>447552</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>417010</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>392251</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>438871</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>57,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>816512</t>
+          <t>817245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>874557</t>
+          <t>875733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>307815</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>284056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>328537</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>261277</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>241022</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>282622</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>242159</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>285280</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>37,88%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>307815</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>285954</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>332574</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>42,47%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>539980</t>
+          <t>538804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>598025</t>
+          <t>597292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>724825</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>724825</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>724825</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>689711</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>724825</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>724825</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>724825</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39778</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32758</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46453</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38062</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31485</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44014</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31727</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43831</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>39778</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32696</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46800</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,97%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67669</t>
+          <t>68727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86827</t>
+          <t>87330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28836</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22161</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35856</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20746</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14794</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27323</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14977</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27081</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28836</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21814</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35918</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40595</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59753</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>351786</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>334110</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>366981</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>513</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>336723</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>319932</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>352263</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>320940</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>352806</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>351786</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>334064</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>367172</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>664782</t>
+          <t>663687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>710103</t>
+          <t>710782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>134038</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>118843</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>151714</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>129149</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113609</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>145940</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>113066</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>144932</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>134038</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>118652</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>151760</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>241592</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286913</t>
+          <t>288008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>485824</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>485824</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>485824</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>703</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>485824</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>485824</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>485824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>149031</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>139973</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>157072</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>131841</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>122490</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139899</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>121788</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>139969</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>149031</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>138757</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>156711</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>81,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267621</t>
+          <t>267992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293458</t>
+          <t>294448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33192</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25151</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42250</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37019</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28961</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46370</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28891</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>47072</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33192</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25512</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>43466</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57625</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83462</t>
+          <t>83091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>519925</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>560415</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>768</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>487730</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>526672</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>485312</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>524695</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>520202</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>559587</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1016482</t>
+          <t>1019468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1072821</t>
+          <t>1074166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -3472,67 +3472,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>196066</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176246</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>216736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>186913</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>166868</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>205810</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>168845</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>208228</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>196066</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>177074</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>216459</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>356035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>413719</t>
+          <t>410733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9843</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11513</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>79,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10427</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5033</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105509</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>97378</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>111439</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>74582</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>67995</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>79962</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>84,19%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,75%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106430</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120791</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>189094</t>
+          <t>178413</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179793</t>
+          <t>169142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197653</t>
+          <t>186531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17379</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25510</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14007</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8627</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20594</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26789</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>32715</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>41325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221809</t>
+          <t>210467</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37454</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32526</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40666</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>35838</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>30974</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39067</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38753</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74592</t>
+          <t>73614</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67511</t>
+          <t>67017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79538</t>
+          <t>78529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5630</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2418</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10558</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4181</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12274</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>143923</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>160044</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>111389</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125669</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154849</t>
+          <t>107006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172418</t>
+          <t>121901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>272672</t>
+          <t>255275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293736</t>
+          <t>278403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18321</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34442</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23243</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16801</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31081</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61568</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
